--- a/fixtures/demo-project/imports/03-welders.xlsx
+++ b/fixtures/demo-project/imports/03-welders.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,6 +412,9 @@
       <c r="D1" t="str">
         <v>WPS Codes</v>
       </c>
+      <c r="E1" t="str">
+        <v>Expires On</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -426,6 +429,9 @@
       <c r="D2" t="str">
         <v>WPS-CS-01,WPS-SS-01</v>
       </c>
+      <c r="E2" t="str">
+        <v>2028-08-13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -440,6 +446,9 @@
       <c r="D3" t="str">
         <v>WPS-CS-01,WPS-SS-01</v>
       </c>
+      <c r="E3" t="str">
+        <v>2028-08-13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -454,6 +463,9 @@
       <c r="D4" t="str">
         <v>WPS-CS-01</v>
       </c>
+      <c r="E4" t="str">
+        <v>2028-08-13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -468,6 +480,9 @@
       <c r="D5" t="str">
         <v>WPS-CS-01</v>
       </c>
+      <c r="E5" t="str">
+        <v>2028-08-13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -482,6 +497,9 @@
       <c r="D6" t="str">
         <v>WPS-CS-01,WPS-SS-01</v>
       </c>
+      <c r="E6" t="str">
+        <v>2028-08-13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -496,6 +514,9 @@
       <c r="D7" t="str">
         <v>WPS-SS-01</v>
       </c>
+      <c r="E7" t="str">
+        <v>2028-08-13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -510,6 +531,9 @@
       <c r="D8" t="str">
         <v>WPS-CS-F01,WPS-SS-F01</v>
       </c>
+      <c r="E8" t="str">
+        <v>2028-08-13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -524,6 +548,9 @@
       <c r="D9" t="str">
         <v>WPS-CS-F01</v>
       </c>
+      <c r="E9" t="str">
+        <v>2028-08-13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -538,6 +565,9 @@
       <c r="D10" t="str">
         <v>WPS-CS-F01,WPS-SS-F01</v>
       </c>
+      <c r="E10" t="str">
+        <v>2028-08-13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -552,10 +582,13 @@
       <c r="D11" t="str">
         <v>WPS-SS-F01</v>
       </c>
+      <c r="E11" t="str">
+        <v>2028-08-13</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
   </ignoredErrors>
 </worksheet>
 </file>